--- a/diseases/d100/1995-1999.xlsx
+++ b/diseases/d100/1995-1999.xlsx
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -16442,7 +16442,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -17242,7 +17242,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -18042,7 +18042,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN92" t="b">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -20442,7 +20442,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -21242,7 +21242,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -22042,7 +22042,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -22842,7 +22842,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -26690,7 +26690,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -27880,7 +27880,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28680,7 +28680,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -29480,7 +29480,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -30280,7 +30280,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -31080,7 +31080,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31880,7 +31880,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32680,7 +32680,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -33480,7 +33480,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -34280,7 +34280,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -35080,7 +35080,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -35880,7 +35880,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -40118,7 +40118,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -41308,7 +41308,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -42108,7 +42108,7 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN208" t="b">
@@ -42908,7 +42908,7 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -43708,7 +43708,7 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN216" t="b">
@@ -44508,7 +44508,7 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -45308,7 +45308,7 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -46108,7 +46108,7 @@
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN228" t="b">
@@ -46908,7 +46908,7 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN232" t="b">
@@ -47708,7 +47708,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -48508,7 +48508,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -49308,7 +49308,7 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN244" t="b">
@@ -55355,7 +55355,7 @@
       </c>
       <c r="AM274" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN274" t="b">
@@ -57564,7 +57564,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -58364,7 +58364,7 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -59164,7 +59164,7 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN293" t="b">
@@ -59964,7 +59964,7 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -60764,7 +60764,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -61564,7 +61564,7 @@
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -62364,7 +62364,7 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -63164,7 +63164,7 @@
       </c>
       <c r="AM313" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN313" t="b">
@@ -63964,7 +63964,7 @@
       </c>
       <c r="AM317" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN317" t="b">
@@ -64764,7 +64764,7 @@
       </c>
       <c r="AM321" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN321" t="b">
@@ -65564,7 +65564,7 @@
       </c>
       <c r="AM325" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN325" t="b">

--- a/diseases/d100/1995-1999.xlsx
+++ b/diseases/d100/1995-1999.xlsx
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -16442,7 +16442,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -17242,7 +17242,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -18042,7 +18042,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN92" t="b">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -20442,7 +20442,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -21242,7 +21242,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -22042,7 +22042,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -22842,7 +22842,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -26690,7 +26690,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -27880,7 +27880,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28680,7 +28680,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -29480,7 +29480,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -30280,7 +30280,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -31080,7 +31080,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31880,7 +31880,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32680,7 +32680,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -33480,7 +33480,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -34280,7 +34280,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -35080,7 +35080,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -35880,7 +35880,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -40118,7 +40118,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -41308,7 +41308,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -42108,7 +42108,7 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN208" t="b">
@@ -42908,7 +42908,7 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -43708,7 +43708,7 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN216" t="b">
@@ -44508,7 +44508,7 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -45308,7 +45308,7 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -46108,7 +46108,7 @@
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN228" t="b">
@@ -46908,7 +46908,7 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN232" t="b">
@@ -47708,7 +47708,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -48508,7 +48508,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -49308,7 +49308,7 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN244" t="b">
@@ -55355,7 +55355,7 @@
       </c>
       <c r="AM274" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN274" t="b">
@@ -57564,7 +57564,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -58364,7 +58364,7 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -59164,7 +59164,7 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN293" t="b">
@@ -59964,7 +59964,7 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -60764,7 +60764,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -61564,7 +61564,7 @@
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -62364,7 +62364,7 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -63164,7 +63164,7 @@
       </c>
       <c r="AM313" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN313" t="b">
@@ -63964,7 +63964,7 @@
       </c>
       <c r="AM317" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN317" t="b">
@@ -64764,7 +64764,7 @@
       </c>
       <c r="AM321" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN321" t="b">
@@ -65564,7 +65564,7 @@
       </c>
       <c r="AM325" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN325" t="b">

--- a/diseases/d100/1995-1999.xlsx
+++ b/diseases/d100/1995-1999.xlsx
@@ -36298,7 +36298,7 @@
         </is>
       </c>
       <c r="AT179" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         </is>
       </c>
       <c r="AT180" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
@@ -50116,7 +50116,7 @@
         </is>
       </c>
       <c r="AT248" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
@@ -50350,7 +50350,7 @@
         </is>
       </c>
       <c r="AT249" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
